--- a/fix/liens-annuaire-sante/ig/CodeSystem-categorie-orientation-sas-codesystem.xlsx
+++ b/fix/liens-annuaire-sante/ig/CodeSystem-categorie-orientation-sas-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:08:20+00:00</t>
+    <t>2026-07-06T12:22:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
